--- a/TFM/clustering/tabla_numeric_cols_clusters.xlsx
+++ b/TFM/clustering/tabla_numeric_cols_clusters.xlsx
@@ -29,13 +29,13 @@
       <b val="1"/>
     </font>
     <font>
+      <color rgb="00000000"/>
+    </font>
+    <font>
       <color rgb="00F1F1F1"/>
     </font>
-    <font>
-      <color rgb="00000000"/>
-    </font>
   </fonts>
-  <fills count="44">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -44,7 +44,177 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0402F"/>
+        <fgColor rgb="00FEE7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0067000D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFECE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF5F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0079040F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEDACA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE0D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007E0610"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDD7C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E32F27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E12D26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FB7050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E53228"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A0510"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E93529"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E83429"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5523A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBE2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0077040F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00940B13"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F24633"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCA78B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCBBA1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00800610"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDD1BE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE7DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEDECF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FC9272"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCA183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C3161B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFECE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FC8565"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FC9B7C"/>
       </patternFill>
     </fill>
     <fill>
@@ -54,202 +224,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0067000D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF5F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6583E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FC8969"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDD4C2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006F020E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE1D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDD7C6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE4D8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00800610"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FC9272"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FC8F6F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCBDA4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDC6B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FB6E4E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FED9C9"/>
+        <fgColor rgb="00FDD0BC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCA98C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AD1117"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCA588"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE5D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEDCCD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075030F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F34A36"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ED392B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E83429"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4503A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A0510"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FB694A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FB7757"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FC9D7F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0069000D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCA183"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE7DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCA98C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F44D38"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FB7B5B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5523A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0073030F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCAE92"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDCDB9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006B010E"/>
       </patternFill>
     </fill>
   </fills>
@@ -292,53 +282,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -704,14 +692,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>active_customer</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -729,40 +717,70 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>em_account_pp</t>
+          <t>z_months_since_entry</t>
         </is>
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>z_months_since_entry</t>
+          <t>z_pct_months_active</t>
         </is>
       </c>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>z_pct_months_active</t>
+          <t>z_new_customer_flag</t>
         </is>
       </c>
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>z_churn_customer_flag</t>
+          <t>z_num_products</t>
         </is>
       </c>
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>z_num_products</t>
+          <t>payment_card</t>
         </is>
       </c>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>z_num_purchased_products</t>
+          <t>account</t>
         </is>
       </c>
       <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>loan</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>investment</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>z_num_families</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>z_active_with_product</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>national</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -856,6 +874,56 @@
           <t>median</t>
         </is>
       </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -869,176 +937,266 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>25.84346291170217</v>
+        <v>0.285119313231763</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>25.33158155146361</v>
+        <v>24.98326639892905</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>24</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>108258.5358045493</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>86290.11</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>31.5536566774983</v>
-      </c>
-      <c r="K4" s="9" t="n">
+        <v>113758.6073889208</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>89195.54999999997</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>30.08538917575062</v>
+      </c>
+      <c r="I4" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="L4" s="10" t="n">
-        <v>0.3218415105441222</v>
+      <c r="J4" s="2" t="n">
+        <v>0.2878367438005992</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>0.02622128726546397</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>0</v>
+      <c r="N4" s="8" t="n">
+        <v>0.9044644185206434</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="11" t="n">
-        <v>1.082721546916998</v>
-      </c>
-      <c r="Q4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="13" t="n">
-        <v>0.01934983485109854</v>
+        <v>1</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0.05310129406514949</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>0.7932364378147511</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>9.562057754828839e-05</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="12" t="n">
+        <v>0.003240475128025329</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="13" t="n">
+        <v>0.8706253585771658</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="14" t="n">
+        <v>0.7953400905208134</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="15" t="n">
+        <v>0.9998406323707528</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>26.38624006346163</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>42.04113437670429</v>
-      </c>
-      <c r="E5" s="16" t="n">
+      <c r="B5" s="6" t="n">
+        <v>0.6113040732554468</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>42.68451441201678</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>108582.2231787007</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>89582.16</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>22.09167231320961</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L5" s="20" t="n">
-        <v>0.8606623808028557</v>
-      </c>
-      <c r="M5" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
+      <c r="F5" s="16" t="n">
+        <v>108803.351976183</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>89195.54999999997</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>22.78266949343678</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0.6083451366021622</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>6.014404498774565e-05</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>1.261010119235569</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="16" t="n">
-        <v>1.87874531061495</v>
-      </c>
-      <c r="Q5" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" s="16" t="n">
-        <v>0.06655208316118263</v>
+        <v>1</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0.2259912490414543</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="19" t="n">
+        <v>0.6891154314583428</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T5" s="20" t="n">
+        <v>0.0002255401687040462</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="21" t="n">
+        <v>0.05058114183469409</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>1.054971657118799</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="22" t="n">
+        <v>0.7066023125385298</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="23" t="n">
+        <v>0.999293307471394</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>26.56818531629983</v>
+      <c r="B6" s="24" t="n">
+        <v>0.2738895084731932</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.89304294289672</v>
+        <v>21.9055164159617</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>21</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>97454.03303863321</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>85265.45999999999</v>
+        <v>99002.76111919593</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>86056.14</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>7.829312080080515</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>7.926935508696322</v>
+        <v>8</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>0.2800798357043767</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="22" t="n">
-        <v>0.3117680467908265</v>
+        <v>0</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>0.0006528302913255175</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0</v>
+        <v>0.7443625384217828</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="23" t="n">
-        <v>0.8431583807911344</v>
-      </c>
-      <c r="Q6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="21" t="n">
-        <v>0.006341388333076805</v>
+        <v>1</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.01559992383646601</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="27" t="n">
+        <v>0.7195277860892746</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0.0002584119903163507</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0.7397247232271578</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="28" t="n">
+        <v>0.7205478334194707</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1046,242 +1204,189 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>24.70202215104388</v>
+        <v>0.2544549969796631</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" s="24" t="n">
-        <v>24.40823138964998</v>
-      </c>
-      <c r="E7" s="25" t="n">
-        <v>23</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>126237.4111029213</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>102747.18</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="26" t="n">
-        <v>23.23499787751322</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.03817388955350597</v>
+        <v>0</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>24.54303141150413</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>108949.0358731291</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>86056.14</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>31.00272669306665</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.2587529364386871</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="31" t="n">
+        <v>0.01562185381569233</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
+      <c r="N7" s="32" t="n">
+        <v>0.875494999664407</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.0001543626751051596</v>
+        <v>1</v>
+      </c>
+      <c r="P7" s="33" t="n">
+        <v>0.03441506141351769</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
+      <c r="R7" s="6" t="n">
+        <v>0.7977381032284045</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T7" s="33" t="n">
+        <v>2.516947446137325e-05</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="34" t="n">
+        <v>0.001191355124505</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="35" t="n">
+        <v>0.8502835760789315</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>0.7992231022216256</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="21" t="n">
+        <v>0.9999496610510773</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>25.72841510468279</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>40.36089734128908</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>39</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>104455.2838638807</v>
-      </c>
-      <c r="G8" s="30" t="n">
-        <v>86056.14</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="31" t="n">
-        <v>23.73482468531911</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="L8" s="32" t="n">
-        <v>0.1099574100234034</v>
+      <c r="B8" s="10" t="n">
+        <v>0.59796565507693</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>41.71027891293183</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>106138.1743749581</v>
+      </c>
+      <c r="G8" s="37" t="n">
+        <v>88116.81</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>22.9147294611554</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>0.5966569527254862</v>
+      </c>
+      <c r="K8" s="39" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1.116544963265671e-05</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
+      <c r="N8" s="40" t="n">
+        <v>1.234016658850852</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="33" t="n">
-        <v>0.02194859685002847</v>
+        <v>1</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>0.2185078493110918</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0001475890278099897</v>
+        <v>0.6722940532815257</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="34" t="n">
-        <v>25.46108219846884</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>25.16036648072548</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>103552.8697896475</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>83399.28</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>32.26143953795174</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="L9" s="36" t="n">
-        <v>0.2913247530306335</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="37" t="n">
-        <v>1.057485950533412</v>
-      </c>
-      <c r="Q9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="38" t="n">
-        <v>0.01258998410670323</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>26.57357777919239</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>42.43762598934794</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="F10" s="39" t="n">
-        <v>111436.4200706601</v>
-      </c>
-      <c r="G10" s="34" t="n">
-        <v>91248.75</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="40" t="n">
-        <v>21.71044199715662</v>
-      </c>
-      <c r="K10" s="41" t="n">
-        <v>19</v>
-      </c>
-      <c r="L10" s="16" t="n">
-        <v>0.8653988159653702</v>
-      </c>
-      <c r="M10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="42" t="n">
-        <v>1.831667621533304</v>
-      </c>
-      <c r="Q10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="43" t="n">
-        <v>0.06590701720881872</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0.0002903016904490744</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.05325919474777249</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="41" t="n">
+        <v>1.023882896764253</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0.6859382327326321</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>0.9989616131841629</v>
+      </c>
+      <c r="AC8" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
